--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260702.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260702.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>42,418,027</t>
+          <t>42,424,027</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>64.19%</t>
+          <t>63.86%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>6.71%</t>
+          <t>6.80%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>21,245,000</t>
+          <t>21,249,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.18%</t>
+          <t>3.10%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>2.45%</t>
+          <t>2.56%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>20,295,286</t>
+          <t>20,298,286</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>2.05%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>2,739,608</t>
+          <t>2,740,608</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.77%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.72%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>2,294,901</t>
+          <t>2,295,901</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.37%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>5,382,296</t>
+          <t>5,383,296</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.60%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.57%</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>12,771,134</t>
+          <t>12,773,134</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.53%</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>5,253,520</t>
+          <t>5,254,520</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.49%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
@@ -1029,51 +1029,51 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>597,600</t>
+          <t>598,600</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>850,349</t>
+          <t>139,482</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>139,482</t>
+          <t>99,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>99,000</t>
+          <t>850,349</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,22 +1129,22 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>310,672</t>
+          <t>136,921</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.41%</t>
         </is>
       </c>
     </row>
@@ -1166,29 +1166,29 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.40%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>136,921</t>
+          <t>310,672</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.39%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.33%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.32%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.29%</t>
         </is>
       </c>
     </row>
@@ -1320,90 +1320,90 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>801,897</t>
+          <t>1,818,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>1,818,000</t>
+          <t>801,897</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>1,186,441</t>
+          <t>44,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>44,000</t>
+          <t>1,187,441</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.24%</t>
         </is>
       </c>
     </row>
@@ -1452,29 +1452,29 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.22%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>144,386</t>
+          <t>10,515,121</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.20%</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>928,659</t>
+          <t>929,659</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>10,513,121</t>
+          <t>144,386</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>493,000</t>
+          <t>3,451,981</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>4,417,578</t>
+          <t>1,367,384</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,39 +1569,39 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>1,367,384</t>
+          <t>4,418,578</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.18%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>3,451,981</t>
+          <t>493,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>2,575,703</t>
+          <t>2,576,703</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>7,110,249</t>
+          <t>7,111,249</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>202607WVHFN6F</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>770,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1701,22 +1701,22 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>202607WVHFN6F</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>770,000</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.12%</t>
         </is>
       </c>
     </row>
@@ -1738,24 +1738,24 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>0.11%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>798,000</t>
+          <t>288,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>4,918,956</t>
+          <t>4,919,956</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1811,39 +1811,39 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>1,547,400</t>
+          <t>798,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.10%</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>288,000</t>
+          <t>1,547,400</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>386,000</t>
+          <t>387,000</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -1943,17 +1943,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>155,000</t>
+          <t>176,000</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>995,121</t>
+          <t>169,000</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>1,743,000</t>
+          <t>64,538</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>169,000</t>
+          <t>155,000</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>64,538</t>
+          <t>995,121</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>176,000</t>
+          <t>1,743,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>252,000</t>
+          <t>329,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2097,17 +2097,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>328,000</t>
+          <t>252,000</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -2119,17 +2119,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>新唐</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>674,000</t>
+          <t>333,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -2141,39 +2141,39 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>台勝科</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>114,000</t>
+          <t>674,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.04%</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>新唐</t>
+          <t>台勝科</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>333,000</t>
+          <t>114,000</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>385,995,294</t>
+          <t>386,890,738</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr"/>
@@ -2235,7 +2235,7 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>465,223,287</t>
+          <t>449,106,287</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr"/>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>-156,222,131</t>
+          <t>-177,841,829</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr"/>
